--- a/sources/hose1.xlsx
+++ b/sources/hose1.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NORTHERN STAR RESOURCES LIMITED</t>
+          <t>OWNER</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KCGM GROWTH PROJECT</t>
+          <t>GROWTH PROJECT</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Slurry Hose - Fimiston SAG Mill Discharge 90Deg Bend</t>
+          <t>Slurry Hose - FIM SAG Mill Discharge 90Deg Bend</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Slurry Hose - Fimiston SAG Mill Discharge 45Deg Bend</t>
+          <t>Slurry Hose - FIM SAG Mill Discharge 45Deg Bend</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Slurry Hose - Fimiston SAG Mill Discharge 90Deg Bend w/ Extension 1</t>
+          <t>Slurry Hose - FIM SAG Mill Discharge 90Deg Bend w/ Extension 1</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Slurry Hose - Fimiston SAG Mill Discharge 90Deg Bend w/ Extension 2</t>
+          <t>Slurry Hose - FIM SAG Mill Discharge 90Deg Bend w/ Extension 2</t>
         </is>
       </c>
       <c r="F53" t="n">
